--- a/Outputs/Correlation/corr_matrix_full.xlsx
+++ b/Outputs/Correlation/corr_matrix_full.xlsx
@@ -143,7 +143,7 @@
     <t xml:space="preserve">Biliverdin</t>
   </si>
   <si>
-    <t xml:space="preserve">Butanoylcarnitine</t>
+    <t xml:space="preserve">Butyrylcarnitine</t>
   </si>
   <si>
     <t xml:space="preserve">CTP</t>

--- a/Outputs/Correlation/corr_matrix_full.xlsx
+++ b/Outputs/Correlation/corr_matrix_full.xlsx
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">0.803845568350531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6500339508738</t>
+    <t xml:space="preserve">0.650033950873801</t>
   </si>
   <si>
     <t xml:space="preserve">0.511050778112373</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">0.558181818181818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60397814172755</t>
+    <t xml:space="preserve">0.603978141727549</t>
   </si>
   <si>
     <t xml:space="preserve">0.696926936388255</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">0.53217768011547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49344324400603</t>
+    <t xml:space="preserve">0.493443244006031</t>
   </si>
   <si>
     <t xml:space="preserve">0.74047619047619</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">0.619020132934035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62958152958153</t>
+    <t xml:space="preserve">0.629581529581529</t>
   </si>
   <si>
     <t xml:space="preserve">0.652597402597403</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">0.34992784992785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32950937950938</t>
+    <t xml:space="preserve">0.329509379509379</t>
   </si>
   <si>
     <t xml:space="preserve">0.483838383838384</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">0.715512265512265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71955266955267</t>
+    <t xml:space="preserve">0.719552669552669</t>
   </si>
   <si>
     <t xml:space="preserve">0.57034632034632</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">0.449747985097584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51053391053391</t>
+    <t xml:space="preserve">0.510533910533911</t>
   </si>
   <si>
     <t xml:space="preserve">0.616955266955267</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">0.276785970682831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64054834054834</t>
+    <t xml:space="preserve">0.640548340548341</t>
   </si>
   <si>
     <t xml:space="preserve">0.431468811928673</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">0.808516833594011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36037533923718</t>
+    <t xml:space="preserve">0.360375339237181</t>
   </si>
   <si>
     <t xml:space="preserve">0.419631929165826</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">-0.270562770562771</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.26948051948052</t>
+    <t xml:space="preserve">-0.269480519480519</t>
   </si>
   <si>
     <t xml:space="preserve">-0.277034101567661</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">0.556677972442718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60798037534703</t>
+    <t xml:space="preserve">0.607980375347031</t>
   </si>
   <si>
     <t xml:space="preserve">0.431344253954967</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">0.617525617303872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77950937950938</t>
+    <t xml:space="preserve">0.779509379509379</t>
   </si>
   <si>
     <t xml:space="preserve">0.706892864508101</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">0.312193362193362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83059163059163</t>
+    <t xml:space="preserve">0.830591630591631</t>
   </si>
   <si>
     <t xml:space="preserve">0.989393939393939</t>
@@ -4967,13 +4967,13 @@
     <t xml:space="preserve">0.540692640692641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3000581531107</t>
+    <t xml:space="preserve">0.300058153110699</t>
   </si>
   <si>
     <t xml:space="preserve">0.641133599633721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66955266955267</t>
+    <t xml:space="preserve">0.669552669552669</t>
   </si>
   <si>
     <t xml:space="preserve">0.516675986303141</t>
@@ -5849,7 +5849,7 @@
     <t xml:space="preserve">0.578499278499279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48953823953824</t>
+    <t xml:space="preserve">0.489538239538239</t>
   </si>
   <si>
     <t xml:space="preserve">0.765997791537178</t>
@@ -6212,7 +6212,7 @@
     <t xml:space="preserve">0.605158734182914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41626995984032</t>
+    <t xml:space="preserve">0.416269959840321</t>
   </si>
   <si>
     <t xml:space="preserve">0.672943722943723</t>
@@ -6917,7 +6917,7 @@
     <t xml:space="preserve">0.516305916305916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49054834054834</t>
+    <t xml:space="preserve">0.490548340548341</t>
   </si>
   <si>
     <t xml:space="preserve">0.673729942208421</t>
@@ -7076,7 +7076,7 @@
     <t xml:space="preserve">0.469471310127043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57990308118084</t>
+    <t xml:space="preserve">0.579903081180841</t>
   </si>
   <si>
     <t xml:space="preserve">0.532251082251082</t>
@@ -7349,7 +7349,7 @@
     <t xml:space="preserve">0.351829137217199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28051948051948</t>
+    <t xml:space="preserve">0.280519480519481</t>
   </si>
   <si>
     <t xml:space="preserve">0.38030303030303</t>
@@ -8003,7 +8003,7 @@
     <t xml:space="preserve">-0.410678210678211</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.7005772005772</t>
+    <t xml:space="preserve">-0.700577200577201</t>
   </si>
   <si>
     <t xml:space="preserve">-0.455655295757878</t>
@@ -8222,7 +8222,7 @@
     <t xml:space="preserve">0.706421356421356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66060606060606</t>
+    <t xml:space="preserve">0.660606060606061</t>
   </si>
   <si>
     <t xml:space="preserve">0.658225108225108</t>
@@ -8327,7 +8327,7 @@
     <t xml:space="preserve">0.539033189033189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77625411045381</t>
+    <t xml:space="preserve">0.776254110453811</t>
   </si>
   <si>
     <t xml:space="preserve">0.668831168831169</t>
@@ -8396,7 +8396,7 @@
     <t xml:space="preserve">0.724458874458874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66053391053391</t>
+    <t xml:space="preserve">0.660533910533911</t>
   </si>
   <si>
     <t xml:space="preserve">0.823232323232323</t>
@@ -8636,7 +8636,7 @@
     <t xml:space="preserve">0.741728318041991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66560812706695</t>
+    <t xml:space="preserve">0.665608127066949</t>
   </si>
   <si>
     <t xml:space="preserve">0.664452799305101</t>
@@ -9368,7 +9368,7 @@
     <t xml:space="preserve">0.75981240981241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73946608946609</t>
+    <t xml:space="preserve">0.739466089466089</t>
   </si>
   <si>
     <t xml:space="preserve">0.720995670995671</t>
@@ -9428,7 +9428,7 @@
     <t xml:space="preserve">0.611471861471861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73336308149801</t>
+    <t xml:space="preserve">0.733363081498011</t>
   </si>
   <si>
     <t xml:space="preserve">-0.289033189033189</t>
@@ -10424,7 +10424,7 @@
     <t xml:space="preserve">0.532562987844382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49327687849754</t>
+    <t xml:space="preserve">0.493276878497539</t>
   </si>
   <si>
     <t xml:space="preserve">0.334766762874502</t>
@@ -11969,7 +11969,7 @@
     <t xml:space="preserve">0.559439835305203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34949494949495</t>
+    <t xml:space="preserve">0.349494949494949</t>
   </si>
   <si>
     <t xml:space="preserve">0.522077922077922</t>
@@ -12125,7 +12125,7 @@
     <t xml:space="preserve">0.638387026212766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52785641674059</t>
+    <t xml:space="preserve">0.527856416740589</t>
   </si>
   <si>
     <t xml:space="preserve">0.27972582972583</t>
@@ -12269,7 +12269,7 @@
     <t xml:space="preserve">0.521789321789322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54949494949495</t>
+    <t xml:space="preserve">0.549494949494949</t>
   </si>
   <si>
     <t xml:space="preserve">0.638961038961039</t>
@@ -12569,13 +12569,13 @@
     <t xml:space="preserve">0.330995116225139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45600869082726</t>
+    <t xml:space="preserve">0.456008690827259</t>
   </si>
   <si>
     <t xml:space="preserve">0.64056301536751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63514980678694</t>
+    <t xml:space="preserve">0.635149806786939</t>
   </si>
   <si>
     <t xml:space="preserve">0.427967613112619</t>
@@ -14387,7 +14387,7 @@
     <t xml:space="preserve">0.334301820125953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63374944705172</t>
+    <t xml:space="preserve">0.633749447051721</t>
   </si>
   <si>
     <t xml:space="preserve">0.333867191540741</t>
@@ -14579,7 +14579,7 @@
     <t xml:space="preserve">0.651298701298701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66948051948052</t>
+    <t xml:space="preserve">0.669480519480519</t>
   </si>
   <si>
     <t xml:space="preserve">0.412682574094233</t>
@@ -15428,7 +15428,7 @@
     <t xml:space="preserve">0.706923393848142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49420614240551</t>
+    <t xml:space="preserve">0.494206142405511</t>
   </si>
   <si>
     <t xml:space="preserve">0.789365796408637</t>
@@ -15485,7 +15485,7 @@
     <t xml:space="preserve">0.469722152564705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31077441156743</t>
+    <t xml:space="preserve">0.310774411567431</t>
   </si>
   <si>
     <t xml:space="preserve">0.369198265580107</t>
@@ -15554,7 +15554,7 @@
     <t xml:space="preserve">0.497619047619048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57957785536355</t>
+    <t xml:space="preserve">0.579577855363551</t>
   </si>
   <si>
     <t xml:space="preserve">0.77979797979798</t>

--- a/Outputs/Correlation/corr_matrix_full.xlsx
+++ b/Outputs/Correlation/corr_matrix_full.xlsx
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">0.803845568350531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650033950873801</t>
+    <t xml:space="preserve">0.6500339508738</t>
   </si>
   <si>
     <t xml:space="preserve">0.511050778112373</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">0.558181818181818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603978141727549</t>
+    <t xml:space="preserve">0.60397814172755</t>
   </si>
   <si>
     <t xml:space="preserve">0.696926936388255</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">0.53217768011547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493443244006031</t>
+    <t xml:space="preserve">0.49344324400603</t>
   </si>
   <si>
     <t xml:space="preserve">0.74047619047619</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">0.619020132934035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629581529581529</t>
+    <t xml:space="preserve">0.62958152958153</t>
   </si>
   <si>
     <t xml:space="preserve">0.652597402597403</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">0.34992784992785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329509379509379</t>
+    <t xml:space="preserve">0.32950937950938</t>
   </si>
   <si>
     <t xml:space="preserve">0.483838383838384</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">0.715512265512265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.719552669552669</t>
+    <t xml:space="preserve">0.71955266955267</t>
   </si>
   <si>
     <t xml:space="preserve">0.57034632034632</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">0.449747985097584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510533910533911</t>
+    <t xml:space="preserve">0.51053391053391</t>
   </si>
   <si>
     <t xml:space="preserve">0.616955266955267</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">0.276785970682831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640548340548341</t>
+    <t xml:space="preserve">0.64054834054834</t>
   </si>
   <si>
     <t xml:space="preserve">0.431468811928673</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">0.808516833594011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360375339237181</t>
+    <t xml:space="preserve">0.36037533923718</t>
   </si>
   <si>
     <t xml:space="preserve">0.419631929165826</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">-0.270562770562771</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.269480519480519</t>
+    <t xml:space="preserve">-0.26948051948052</t>
   </si>
   <si>
     <t xml:space="preserve">-0.277034101567661</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">0.556677972442718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607980375347031</t>
+    <t xml:space="preserve">0.60798037534703</t>
   </si>
   <si>
     <t xml:space="preserve">0.431344253954967</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">0.617525617303872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779509379509379</t>
+    <t xml:space="preserve">0.77950937950938</t>
   </si>
   <si>
     <t xml:space="preserve">0.706892864508101</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">0.312193362193362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830591630591631</t>
+    <t xml:space="preserve">0.83059163059163</t>
   </si>
   <si>
     <t xml:space="preserve">0.989393939393939</t>
@@ -4967,13 +4967,13 @@
     <t xml:space="preserve">0.540692640692641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300058153110699</t>
+    <t xml:space="preserve">0.3000581531107</t>
   </si>
   <si>
     <t xml:space="preserve">0.641133599633721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669552669552669</t>
+    <t xml:space="preserve">0.66955266955267</t>
   </si>
   <si>
     <t xml:space="preserve">0.516675986303141</t>
@@ -5849,7 +5849,7 @@
     <t xml:space="preserve">0.578499278499279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489538239538239</t>
+    <t xml:space="preserve">0.48953823953824</t>
   </si>
   <si>
     <t xml:space="preserve">0.765997791537178</t>
@@ -6212,7 +6212,7 @@
     <t xml:space="preserve">0.605158734182914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416269959840321</t>
+    <t xml:space="preserve">0.41626995984032</t>
   </si>
   <si>
     <t xml:space="preserve">0.672943722943723</t>
@@ -6917,7 +6917,7 @@
     <t xml:space="preserve">0.516305916305916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490548340548341</t>
+    <t xml:space="preserve">0.49054834054834</t>
   </si>
   <si>
     <t xml:space="preserve">0.673729942208421</t>
@@ -7076,7 +7076,7 @@
     <t xml:space="preserve">0.469471310127043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579903081180841</t>
+    <t xml:space="preserve">0.57990308118084</t>
   </si>
   <si>
     <t xml:space="preserve">0.532251082251082</t>
@@ -7349,7 +7349,7 @@
     <t xml:space="preserve">0.351829137217199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280519480519481</t>
+    <t xml:space="preserve">0.28051948051948</t>
   </si>
   <si>
     <t xml:space="preserve">0.38030303030303</t>
@@ -8003,7 +8003,7 @@
     <t xml:space="preserve">-0.410678210678211</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.700577200577201</t>
+    <t xml:space="preserve">-0.7005772005772</t>
   </si>
   <si>
     <t xml:space="preserve">-0.455655295757878</t>
@@ -8222,7 +8222,7 @@
     <t xml:space="preserve">0.706421356421356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.660606060606061</t>
+    <t xml:space="preserve">0.66060606060606</t>
   </si>
   <si>
     <t xml:space="preserve">0.658225108225108</t>
@@ -8327,7 +8327,7 @@
     <t xml:space="preserve">0.539033189033189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776254110453811</t>
+    <t xml:space="preserve">0.77625411045381</t>
   </si>
   <si>
     <t xml:space="preserve">0.668831168831169</t>
@@ -8396,7 +8396,7 @@
     <t xml:space="preserve">0.724458874458874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.660533910533911</t>
+    <t xml:space="preserve">0.66053391053391</t>
   </si>
   <si>
     <t xml:space="preserve">0.823232323232323</t>
@@ -8636,7 +8636,7 @@
     <t xml:space="preserve">0.741728318041991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665608127066949</t>
+    <t xml:space="preserve">0.66560812706695</t>
   </si>
   <si>
     <t xml:space="preserve">0.664452799305101</t>
@@ -9368,7 +9368,7 @@
     <t xml:space="preserve">0.75981240981241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.739466089466089</t>
+    <t xml:space="preserve">0.73946608946609</t>
   </si>
   <si>
     <t xml:space="preserve">0.720995670995671</t>
@@ -9428,7 +9428,7 @@
     <t xml:space="preserve">0.611471861471861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.733363081498011</t>
+    <t xml:space="preserve">0.73336308149801</t>
   </si>
   <si>
     <t xml:space="preserve">-0.289033189033189</t>
@@ -10424,7 +10424,7 @@
     <t xml:space="preserve">0.532562987844382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493276878497539</t>
+    <t xml:space="preserve">0.49327687849754</t>
   </si>
   <si>
     <t xml:space="preserve">0.334766762874502</t>
@@ -11969,7 +11969,7 @@
     <t xml:space="preserve">0.559439835305203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349494949494949</t>
+    <t xml:space="preserve">0.34949494949495</t>
   </si>
   <si>
     <t xml:space="preserve">0.522077922077922</t>
@@ -12125,7 +12125,7 @@
     <t xml:space="preserve">0.638387026212766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527856416740589</t>
+    <t xml:space="preserve">0.52785641674059</t>
   </si>
   <si>
     <t xml:space="preserve">0.27972582972583</t>
@@ -12269,7 +12269,7 @@
     <t xml:space="preserve">0.521789321789322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549494949494949</t>
+    <t xml:space="preserve">0.54949494949495</t>
   </si>
   <si>
     <t xml:space="preserve">0.638961038961039</t>
@@ -12569,13 +12569,13 @@
     <t xml:space="preserve">0.330995116225139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456008690827259</t>
+    <t xml:space="preserve">0.45600869082726</t>
   </si>
   <si>
     <t xml:space="preserve">0.64056301536751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635149806786939</t>
+    <t xml:space="preserve">0.63514980678694</t>
   </si>
   <si>
     <t xml:space="preserve">0.427967613112619</t>
@@ -14387,7 +14387,7 @@
     <t xml:space="preserve">0.334301820125953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633749447051721</t>
+    <t xml:space="preserve">0.63374944705172</t>
   </si>
   <si>
     <t xml:space="preserve">0.333867191540741</t>
@@ -14579,7 +14579,7 @@
     <t xml:space="preserve">0.651298701298701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669480519480519</t>
+    <t xml:space="preserve">0.66948051948052</t>
   </si>
   <si>
     <t xml:space="preserve">0.412682574094233</t>
@@ -15428,7 +15428,7 @@
     <t xml:space="preserve">0.706923393848142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494206142405511</t>
+    <t xml:space="preserve">0.49420614240551</t>
   </si>
   <si>
     <t xml:space="preserve">0.789365796408637</t>
@@ -15485,7 +15485,7 @@
     <t xml:space="preserve">0.469722152564705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310774411567431</t>
+    <t xml:space="preserve">0.31077441156743</t>
   </si>
   <si>
     <t xml:space="preserve">0.369198265580107</t>
@@ -15554,7 +15554,7 @@
     <t xml:space="preserve">0.497619047619048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579577855363551</t>
+    <t xml:space="preserve">0.57957785536355</t>
   </si>
   <si>
     <t xml:space="preserve">0.77979797979798</t>
